--- a/tools/sheets/player.xlsx
+++ b/tools/sheets/player.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PlayerParts" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_help" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EquipSlots" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_help" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -793,7 +794,81 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>slot_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>bag</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>가방</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>무기</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>머리</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>몸</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -855,6 +930,13 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EquipSlots: 장비창 칸 (slot_id, 이름). 행 순서대로 보임. 아이템의 equip_slot 이 이 slot_id. 지금 칸은 더미 (가방 외에는 TODO 기획)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/sheets/player.xlsx
+++ b/tools/sheets/player.xlsx
@@ -794,7 +794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -808,6 +808,21 @@
           <t>name</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>col</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -820,29 +835,62 @@
           <t>가방</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>bag</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>weapon</t>
+          <t>head</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>무기</t>
-        </is>
+          <t>머리</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>left_hand</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>머리</t>
-        </is>
+          <t>왼손</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -855,6 +903,86 @@
         <is>
           <t>몸</t>
         </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>right_hand</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>오른손</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>left_leg</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>왼다리</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>leg</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>right_leg</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>오른다리</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>leg</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -881,6 +1009,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -933,7 +1062,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EquipSlots: 장비창 칸 (slot_id, 이름). 행 순서대로 보임. 아이템의 equip_slot 이 이 slot_id. 지금 칸은 더미 (가방 외에는 TODO 기획)</t>
+          <t>EquipSlots: 장비창 칸. kind = 들어가는 종류 (아이템 equip_slot 과 같으면 장착). kind 가 hand 인 칸(손)은 어떤 아이템이든 들 수 있고, 손에 든 것은 소지품 칸을 차지하지 않는다. col·row = 장비창 격자 위치 (0.5 단위 가능)</t>
         </is>
       </c>
     </row>

--- a/tools/sheets/player.xlsx
+++ b/tools/sheets/player.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PlayerParts" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EquipSlots" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_help" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traits" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_help" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,12 +33,17 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDE7F5"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,9 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -996,7 +1003,1665 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:J41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>trait_id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>polarity</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>conflicts</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>selectable</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>high_intellect</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>고지능자</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>대화</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>지식 관련 d20 판정 +2</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>효과·비용 확정. 지식 태그 체계 미정</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>well_read</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>박학다식</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>대화</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>역사·과학 등 지식 판정 +1</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>robust_body</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>강골</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>신체</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>모든 신체 부위 최대 체력 +10%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>strong_stomach</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>튼튼한 위장</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>생존</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>상한 음식의 부정적 효과 감소</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>athlete</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>운동선수</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>신체</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>달리기 속도 +10%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>reflexes</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>반사신경</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>전투</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>회피 액션의 허용 타이밍 범위 증가</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>일부 확정</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>이름 확정, 수치 미정. 이동 속도가 아니라 회피 입력 허용 시간</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>marksman</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>명사수</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>전투</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>무기 공격 명중률 +10%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>powerful</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>괴력</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>신체</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>최대 소지 무게 증가</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>light_eater</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>소식가</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>생존</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>포만감 감소 속도 −20%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>water_saver</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>절수 체질</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>생존</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>수분 감소 속도 −20%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sound_sleeper</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>숙면 체질</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>생존</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>수면 회복 효율 증가</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>clean_body</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>청결 체질</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>생존</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>위생 감소 속도 −20%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>iron_mind</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>강철 멘탈</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>정신</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>멘탈 감소량 −20%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>brave</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>용감함</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>정신</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>괴물 조우 시 공포 상태이상 저항 확률 증가</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>일부 확정</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>명칭·효과 방향 확정, 확률 미정. 공포에만 (공황 장애 제외)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>insightful</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>통찰력</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>대화</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>의도 파악·거짓말 간파 판정 +2</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>persuasive</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>달변가</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>대화</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>설득 관련 d20 판정 +2</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>lucky</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>행운아</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-6</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>대화</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>대화 d20 대실패 위험 완화</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>d20 대실패(1) 규칙과 충돌 — 예외 허용을 정하기 전까지 선택 불가</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>medical_knowledge</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>약학 지식</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>대화</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>약품·의료 관련 d20 판정 +2</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>night_owl</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>야행성</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>정신</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>야간 멘탈 감소량 감소</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>survivalist</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>생존 전문가</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>탐험</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>생존·환경 조사 관련 d20 판정 +2</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>heavy_smoker</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>골초</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>생존</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>주기적으로 담배를 피우지 않으면 금단현상 발생</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>효과·보상 확정. 흡연 간격·해소 조건 미정 (상태이상 withdrawal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>heavy_drinker</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>애주가</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>생존</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>일정 기간 음주하지 않으면 금단 상태이상 발생</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>골초와 금단 시스템 공유, 아이템·조건은 따로</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>big_eater</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>대식가</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>생존</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>포만감 감소 속도 +25%</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>excess_sweating</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>다한증</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>생존</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>수분·위생 감소 속도 증가</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>insomnia</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>불면증</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>생존</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>수면 회복 효율 감소</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>light_sleep</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>얕은 잠</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>생존</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>수면 중 방해받기 쉬움</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>콘텐츠 준비 전 선택 불가</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>frail_body</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>허약 체질</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>6</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>신체</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>모든 신체 부위 최대 체력 −10%</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>weak_lifter</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>약골</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>신체</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>최대 소지 무게 감소</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>slow_reflexes</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>둔한 몸</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>6</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>전투</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>회피 액션 허용 시간 감소</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>반사신경과 동시 선택 여부 미정</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>slow_mover</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>느림보</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>신체</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>걷기·달리기 속도 −10%</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>nearsighted</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>근시</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>탐험</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>필드 시야 범위 감소, 안경으로 보완 가능</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>콘텐츠 준비 전 선택 불가</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>hearing_impairment</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>청각 장애</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>탐험</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>청각 단서 및 적 소리 인지 제약</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>콘텐츠 준비 전 선택 불가</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>germaphobe</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>결벽증</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>정신</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>위생이 낮을 때 멘탈 추가 감소</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>coward</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>겁쟁이</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>정신</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>괴물 조우 시 멘탈 추가 감소</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>용감함과 동시 선택 여부 미정</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>fragile_mind</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>유리 멘탈</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>5</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>정신</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>멘탈 감소량 +20%</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>pessimist</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>비관주의자</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>정신</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>부정적 사건에서 멘탈 추가 감소</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>social_misfit</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>사회 부적응자</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>대화</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>일부 설득·사교 d20 판정 −2</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>illiterate</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>문맹</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>6</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>대화</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>일부 문서·조사·대화 선택지 이용 불가</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>콘텐츠 준비 전 선택 불가</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>forgetful</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>건망증</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>대화</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>기억·정보 관련 d20 판정 −2</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>unlucky</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>불운아</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>5</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>대화</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>대화 d20 대실패 위험 증가</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>후보</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1009,7 +2674,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1063,6 +2727,42 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>EquipSlots: 장비창 칸. kind = 들어가는 종류 (아이템 equip_slot 과 같으면 장착). kind 가 hand 인 칸(손)은 어떤 아이템이든 들 수 있고, 손에 든 것은 소지품 칸을 차지하지 않는다. col·row = 장비창 격자 위치 (0.5 단위 가능)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>[특성] Traits: 캐릭터 생성 때 고르는 특성 + 사건·거래로 얻는 특성 (기획 tevah_character_creation_status_effects_spec_v0.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  polarity: positive(긍정) / negative(부정). points: 생성 포인트 — 긍정은 소비(음수, 예: 고지능자 -6), 부정은 획득(양수, 예: 골초 +2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  category: 화면 분류 (신체·정신·생존·탐험·대화·전투). conflicts: 같이 고를 수 없는 trait_id (쉼표). selectable: 1 = 생성 화면에서 고를 수 있음, 0 = 못 고름 (사건·거래로만)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  state: 확정 / 일부 확정 / 후보 (기획 상태). note: 미정 사항. 효과는 아직 설명뿐 (실제 효과는 TODO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Player·Npcs 의 traits 열과 조건 trait:id 는 여기의 trait_id 를 쓴다 (없는 이름이면 변환 경고)</t>
         </is>
       </c>
     </row>

--- a/tools/sheets/player.xlsx
+++ b/tools/sheets/player.xlsx
@@ -1180,6 +1180,11 @@
           <t>모든 신체 부위 최대 체력 +10%</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>frail_body</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
@@ -1256,6 +1261,11 @@
           <t>달리기 속도 +10%</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>slow_mover</t>
+        </is>
+      </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
@@ -1294,6 +1304,11 @@
           <t>회피 액션의 허용 타이밍 범위 증가</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>slow_reflexes</t>
+        </is>
+      </c>
       <c r="H7" t="n">
         <v>1</v>
       </c>
@@ -1375,6 +1390,11 @@
           <t>최대 소지 무게 증가</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>weak_lifter</t>
+        </is>
+      </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
@@ -1413,6 +1433,11 @@
           <t>포만감 감소 속도 −20%</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>big_eater</t>
+        </is>
+      </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
@@ -1451,6 +1476,11 @@
           <t>수분 감소 속도 −20%</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>excess_sweating</t>
+        </is>
+      </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
@@ -1489,6 +1519,11 @@
           <t>수면 회복 효율 증가</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>insomnia, light_sleep</t>
+        </is>
+      </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
@@ -1527,6 +1562,11 @@
           <t>위생 감소 속도 −20%</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>excess_sweating</t>
+        </is>
+      </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
@@ -1565,6 +1605,11 @@
           <t>멘탈 감소량 −20%</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>fragile_mind</t>
+        </is>
+      </c>
       <c r="H14" t="n">
         <v>1</v>
       </c>
@@ -1603,6 +1648,11 @@
           <t>괴물 조우 시 공포 상태이상 저항 확률 증가</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>coward</t>
+        </is>
+      </c>
       <c r="H15" t="n">
         <v>1</v>
       </c>
@@ -1684,6 +1734,11 @@
           <t>설득 관련 d20 판정 +2</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>social_misfit</t>
+        </is>
+      </c>
       <c r="H17" t="n">
         <v>1</v>
       </c>
@@ -1722,6 +1777,11 @@
           <t>대화 d20 대실패 위험 완화</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>unlucky</t>
+        </is>
+      </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
@@ -1965,6 +2025,11 @@
           <t>포만감 감소 속도 +25%</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>light_eater</t>
+        </is>
+      </c>
       <c r="H24" t="n">
         <v>1</v>
       </c>
@@ -2003,6 +2068,11 @@
           <t>수분·위생 감소 속도 증가</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>water_saver, clean_body</t>
+        </is>
+      </c>
       <c r="H25" t="n">
         <v>1</v>
       </c>
@@ -2041,6 +2111,11 @@
           <t>수면 회복 효율 감소</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>sound_sleeper</t>
+        </is>
+      </c>
       <c r="H26" t="n">
         <v>1</v>
       </c>
@@ -2079,6 +2154,11 @@
           <t>수면 중 방해받기 쉬움</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>sound_sleeper</t>
+        </is>
+      </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
@@ -2122,6 +2202,11 @@
           <t>모든 신체 부위 최대 체력 −10%</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>robust_body</t>
+        </is>
+      </c>
       <c r="H28" t="n">
         <v>1</v>
       </c>
@@ -2160,6 +2245,11 @@
           <t>최대 소지 무게 감소</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>powerful</t>
+        </is>
+      </c>
       <c r="H29" t="n">
         <v>1</v>
       </c>
@@ -2198,6 +2288,11 @@
           <t>회피 액션 허용 시간 감소</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>reflexes</t>
+        </is>
+      </c>
       <c r="H30" t="n">
         <v>1</v>
       </c>
@@ -2241,6 +2336,11 @@
           <t>걷기·달리기 속도 −10%</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>athlete</t>
+        </is>
+      </c>
       <c r="H31" t="n">
         <v>1</v>
       </c>
@@ -2403,6 +2503,11 @@
           <t>괴물 조우 시 멘탈 추가 감소</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>brave</t>
+        </is>
+      </c>
       <c r="H35" t="n">
         <v>1</v>
       </c>
@@ -2446,6 +2551,11 @@
           <t>멘탈 감소량 +20%</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>iron_mind</t>
+        </is>
+      </c>
       <c r="H36" t="n">
         <v>1</v>
       </c>
@@ -2522,6 +2632,11 @@
           <t>일부 설득·사교 d20 판정 −2</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>persuasive</t>
+        </is>
+      </c>
       <c r="H38" t="n">
         <v>1</v>
       </c>
@@ -2639,6 +2754,11 @@
       <c r="F41" t="inlineStr">
         <is>
           <t>대화 d20 대실패 위험 증가</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>lucky</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -2730,7 +2850,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>

--- a/tools/sheets/player.xlsx
+++ b/tools/sheets/player.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>주인공 1</t>
+          <t>루이스</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
